--- a/backtest_runs/20260410_193731/by_symbol/ASTL/ASTL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ASTL/ASTL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-4439.610000000005</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>98308.72000000002</v>
@@ -679,7 +679,7 @@
         <v>-5708.070000000003</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>92600.65000000001</v>
@@ -817,7 +817,7 @@
         <v>-2184.570000000003</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>97040.25999999999</v>
@@ -909,7 +909,7 @@
         <v>-1479.870000000006</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>98097.31</v>
@@ -955,7 +955,7 @@
         <v>-5989.949999999997</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>92107.36</v>
@@ -1001,7 +1001,7 @@
         <v>-493.290000000002</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>91614.07000000001</v>
@@ -1047,7 +1047,7 @@
         <v>-1691.280000000002</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>89922.79000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-3805.379999999994</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>91895.95000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-2607.389999999994</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>89499.97000000002</v>
@@ -1415,7 +1415,7 @@
         <v>-1620.80999999999</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>93093.94000000002</v>
@@ -1461,7 +1461,7 @@
         <v>-1902.69000000001</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>91191.25</v>
@@ -1553,7 +1553,7 @@
         <v>-845.6399999999945</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>90697.96000000002</v>
@@ -1645,7 +1645,7 @@
         <v>-986.580000000004</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>99788.59000000001</v>
